--- a/modelo/Plantilla.xlsx
+++ b/modelo/Plantilla.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguel/Documents/GitHub/doc-generator/modelo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE1BD27-E7D5-C542-843C-68EFC43A65C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C19A2C9-8702-854E-BDA7-F4A197BC418E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -319,7 +319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -348,6 +348,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -367,15 +375,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -862,21 +865,21 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="18">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
     </row>
     <row r="6" spans="1:13" ht="16">
       <c r="A6" s="2" t="s">
@@ -1104,19 +1107,19 @@
       <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="F12" s="19"/>
-      <c r="G12" s="20" t="s">
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="25"/>
+      <c r="G12" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="20"/>
+      <c r="H12" s="26"/>
       <c r="I12" s="7" t="s">
         <v>2</v>
       </c>
@@ -1183,15 +1186,15 @@
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
-      <c r="E14" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
+      <c r="E14" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
       <c r="L14" s="8" t="s">
         <v>2</v>
       </c>
@@ -1212,15 +1215,15 @@
       <c r="D15" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
+      <c r="E15" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
       <c r="L15" s="8" t="s">
         <v>2</v>
       </c>
@@ -1241,15 +1244,15 @@
       <c r="D16" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
+      <c r="E16" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
       <c r="L16" s="8" t="s">
         <v>2</v>
       </c>
@@ -1778,19 +1781,19 @@
       <c r="A30" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="23"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
       <c r="M30" s="12" t="s">
         <v>2</v>
       </c>
@@ -1879,15 +1882,15 @@
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="27"/>
-      <c r="K34" s="27"/>
+      <c r="E34" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
       <c r="L34" s="2" t="s">
         <v>2</v>
       </c>
@@ -1940,19 +1943,19 @@
       <c r="A36" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B36" s="23" t="s">
+      <c r="B36" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
       <c r="M36" s="12" t="s">
         <v>2</v>
       </c>
@@ -1991,15 +1994,15 @@
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="27"/>
-      <c r="K38" s="27"/>
+      <c r="E38" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
       <c r="L38" s="2" t="s">
         <v>2</v>
       </c>
@@ -2016,15 +2019,15 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="27"/>
-      <c r="J39" s="27"/>
-      <c r="K39" s="27"/>
+      <c r="E39" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
       <c r="L39" s="2" t="s">
         <v>2</v>
       </c>
@@ -2041,15 +2044,15 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
+      <c r="E40" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
       <c r="L40" s="2" t="s">
         <v>2</v>
       </c>
@@ -2102,19 +2105,19 @@
       <c r="A42" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="23" t="s">
+      <c r="B42" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-      <c r="J42" s="23"/>
-      <c r="K42" s="23"/>
-      <c r="L42" s="23"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
       <c r="M42" s="12" t="s">
         <v>2</v>
       </c>
@@ -2128,15 +2131,15 @@
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
+      <c r="E43" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
       <c r="L43" s="2" t="s">
         <v>2</v>
       </c>
@@ -2190,15 +2193,15 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="27"/>
-      <c r="J45" s="27"/>
-      <c r="K45" s="27"/>
+      <c r="E45" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
       <c r="L45" s="2" t="s">
         <v>2</v>
       </c>
@@ -2215,15 +2218,15 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
-      <c r="E46" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
+      <c r="E46" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
       <c r="L46" s="2" t="s">
         <v>2</v>
       </c>
@@ -2276,19 +2279,19 @@
       <c r="A48" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B48" s="23" t="s">
+      <c r="B48" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C48" s="23"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="23"/>
-      <c r="G48" s="23"/>
-      <c r="H48" s="23"/>
-      <c r="I48" s="23"/>
-      <c r="J48" s="23"/>
-      <c r="K48" s="23"/>
-      <c r="L48" s="23"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
       <c r="M48" s="12" t="s">
         <v>2</v>
       </c>
@@ -2533,19 +2536,19 @@
       <c r="A55" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
       <c r="G55" s="3"/>
-      <c r="H55" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="I55" s="25"/>
-      <c r="J55" s="26"/>
+      <c r="H55" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="I55" s="20"/>
+      <c r="J55" s="21"/>
       <c r="K55" s="2" t="s">
         <v>7</v>
       </c>
@@ -2706,19 +2709,19 @@
       <c r="A60" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B60" s="23" t="s">
+      <c r="B60" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C60" s="23"/>
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
-      <c r="F60" s="23"/>
-      <c r="G60" s="23"/>
-      <c r="H60" s="23"/>
-      <c r="I60" s="23"/>
-      <c r="J60" s="23"/>
-      <c r="K60" s="23"/>
-      <c r="L60" s="23"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="16"/>
+      <c r="H60" s="16"/>
+      <c r="I60" s="16"/>
+      <c r="J60" s="16"/>
+      <c r="K60" s="16"/>
+      <c r="L60" s="16"/>
       <c r="M60" s="12" t="s">
         <v>2</v>
       </c>
@@ -2802,13 +2805,13 @@
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
-      <c r="E63" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="27"/>
-      <c r="I63" s="27"/>
+      <c r="E63" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F63" s="17"/>
+      <c r="G63" s="17"/>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
       <c r="J63" s="2" t="s">
         <v>2</v>
       </c>
@@ -2835,13 +2838,13 @@
       <c r="D64" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E64" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="F64" s="28"/>
-      <c r="G64" s="28"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="28"/>
+      <c r="E64" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="F64" s="18"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="18"/>
+      <c r="I64" s="18"/>
       <c r="J64" s="2" t="s">
         <v>2</v>
       </c>
@@ -2897,24 +2900,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="F57:K57"/>
-    <mergeCell ref="B60:L60"/>
-    <mergeCell ref="E62:I62"/>
-    <mergeCell ref="E63:I63"/>
-    <mergeCell ref="E64:I64"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="E34:K34"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="E37:K37"/>
-    <mergeCell ref="E38:K38"/>
-    <mergeCell ref="E39:K39"/>
-    <mergeCell ref="E40:K40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="E43:K43"/>
-    <mergeCell ref="E45:K45"/>
-    <mergeCell ref="E46:K46"/>
-    <mergeCell ref="B48:L48"/>
+  <mergeCells count="31">
     <mergeCell ref="E33:K33"/>
     <mergeCell ref="A5:M5"/>
     <mergeCell ref="E8:K8"/>
@@ -2928,6 +2914,24 @@
     <mergeCell ref="E31:K31"/>
     <mergeCell ref="E32:K32"/>
     <mergeCell ref="E10:G10"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="E34:K34"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="E37:K37"/>
+    <mergeCell ref="E38:K38"/>
+    <mergeCell ref="E39:K39"/>
+    <mergeCell ref="E40:K40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="E43:K43"/>
+    <mergeCell ref="E45:K45"/>
+    <mergeCell ref="E46:K46"/>
+    <mergeCell ref="B48:L48"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="F57:K57"/>
+    <mergeCell ref="B60:L60"/>
+    <mergeCell ref="E62:I62"/>
+    <mergeCell ref="E63:I63"/>
+    <mergeCell ref="E64:I64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="portrait" r:id="rId1"/>
